--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>707427-14-CM25</t>
+          <t>1965-107-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2439.16</v>
+        <v>8402.879999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1965-107-CM25</t>
+          <t>707427-14-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8402.879999999999</v>
+        <v>2439.16</v>
       </c>
     </row>
     <row r="18">
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4305-48-CM25</t>
+          <t>1038-46-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1709.74</v>
+        <v>17286.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1038-46-CM25</t>
+          <t>4305-48-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>17286.08</v>
+        <v>1709.74</v>
       </c>
     </row>
     <row r="24">
@@ -2165,7 +2165,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1038-86-CM25</t>
+          <t>1965-233-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>351.66</v>
+        <v>8440.709999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1965-233-CM25</t>
+          <t>3367-50-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.927.400-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8440.709999999999</v>
+        <v>198.39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3367-50-CM25</t>
+          <t>1038-86-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.927.400-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>198.39</v>
+        <v>351.66</v>
       </c>
     </row>
     <row r="32">
@@ -3995,7 +3995,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1080095-734-CM25</t>
+          <t>1080094-3084-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1866.77</v>
+        <v>2319.32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1080089-9006-CM25</t>
+          <t>1080095-734-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3394.13</v>
+        <v>1866.77</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1080094-3084-CM25</t>
+          <t>1080089-9006-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2319.32</v>
+        <v>3394.13</v>
       </c>
     </row>
     <row r="62">
@@ -4239,7 +4239,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4305-175-CM25</t>
+          <t>3407-312-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.101.470-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>924.53</v>
+        <v>2532.42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3407-312-CM25</t>
+          <t>4305-175-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.101.470-8</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2532.42</v>
+        <v>924.53</v>
       </c>
     </row>
     <row r="65">
@@ -4483,7 +4483,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1080095-774-CM25</t>
+          <t>1965-684-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4503,17 +4503,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13735.37</v>
+        <v>6690.53</v>
       </c>
     </row>
     <row r="68">
@@ -4605,7 +4605,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1080089-9029-CM25</t>
+          <t>1080095-774-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>35279.2</v>
+        <v>13735.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1965-684-CM25</t>
+          <t>1080089-9029-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6690.53</v>
+        <v>35279.2</v>
       </c>
     </row>
     <row r="71">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4971,7 +4971,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3367-159-CM25</t>
+          <t>5221-147-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.927.400-8</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5026,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1861.96</v>
+        <v>5274.79</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5221-147-CM25</t>
+          <t>3367-159-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5052,17 +5052,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.927.400-8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>5274.79</v>
+        <v>1861.96</v>
       </c>
     </row>
     <row r="77">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6008,7 +6008,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>517903-28-CM26</t>
+          <t>707427-17-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6028,17 +6028,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.114.000-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>EMDN-RMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6056,24 +6056,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>117275.14</v>
+        <v>3430.73</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>707427-17-CM26</t>
+          <t>517903-28-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6093,17 +6089,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.114.000-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6121,14 +6117,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3430.73</v>
+        <v>117275.14</v>
       </c>
     </row>
     <row r="94">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE MAGALLANES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6983,6 +6983,250 @@
       </c>
       <c r="M107" s="2" t="n">
         <v>2570.68</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>661-30-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>61.802.012-6</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>2844.23</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1079445-607-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>60.505.628-8</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>22480.49</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2019-69-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>60.511.122-k</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>1744.43</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2019-72-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>60.511.122-k</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>1642.93</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6182,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6243,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6304,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6365,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6426,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6487,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6548,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6609,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6670,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6731,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6792,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6853,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6914,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6975,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7036,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7097,7 +7517,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7158,7 +7582,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7219,7 +7647,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2269,7 +2269,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1965-233-CM25</t>
+          <t>3367-50-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.927.400-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8440.709999999999</v>
+        <v>198.39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3367-50-CM25</t>
+          <t>1038-86-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.927.400-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>198.39</v>
+        <v>351.66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1038-86-CM25</t>
+          <t>1965-233-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>351.66</v>
+        <v>8440.709999999999</v>
       </c>
     </row>
     <row r="32">
@@ -2529,7 +2529,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>935-5820-CM25</t>
+          <t>935-5821-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>607.08</v>
+        <v>4763.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>935-5821-CM25</t>
+          <t>935-5820-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4763.27</v>
+        <v>607.08</v>
       </c>
     </row>
     <row r="35">
@@ -2919,7 +2919,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>855-180-CM25</t>
+          <t>3229-2401-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.102.026-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3130.41</v>
+        <v>1728.92</v>
       </c>
     </row>
     <row r="40">
@@ -3049,7 +3049,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3229-2401-CM25</t>
+          <t>855-180-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.102.026-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1728.92</v>
+        <v>3130.41</v>
       </c>
     </row>
     <row r="42">
@@ -3504,7 +3504,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1965-485-CM25</t>
+          <t>707427-54-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>860.1900000000001</v>
+        <v>1746.98</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>707427-54-CM25</t>
+          <t>1965-485-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1746.98</v>
+        <v>860.1900000000001</v>
       </c>
     </row>
     <row r="50">
@@ -3829,7 +3829,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1965-618-CM25</t>
+          <t>1080094-3072-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3849,17 +3849,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>7092.07</v>
+        <v>7003.73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1080094-3072-CM25</t>
+          <t>1965-618-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7003.73</v>
+        <v>7092.07</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1080095-659-CM25</t>
+          <t>1080089-8958-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>15745.92</v>
+        <v>34812.02</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1080089-8958-CM25</t>
+          <t>1080095-659-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>34812.02</v>
+        <v>15745.92</v>
       </c>
     </row>
     <row r="57">
@@ -4479,7 +4479,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3407-312-CM25</t>
+          <t>4305-175-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.101.470-8</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2532.42</v>
+        <v>924.53</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4305-175-CM25</t>
+          <t>3407-312-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.101.470-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>924.53</v>
+        <v>2532.42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4305-176-CM25</t>
+          <t>3367-145-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.927.400-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6992.09</v>
+        <v>2008.12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3367-145-CM25</t>
+          <t>4305-176-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.927.400-8</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2008.12</v>
+        <v>6992.09</v>
       </c>
     </row>
     <row r="67">
@@ -4804,7 +4804,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1080094-3090-CM25</t>
+          <t>1080095-774-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6570.98</v>
+        <v>13735.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1080095-774-CM25</t>
+          <t>1080089-9029-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>13735.37</v>
+        <v>35279.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1080089-9029-CM25</t>
+          <t>1080094-3090-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>35279.2</v>
+        <v>6570.98</v>
       </c>
     </row>
     <row r="71">
@@ -5519,7 +5519,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3229-10368-CM25</t>
+          <t>3412-246-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5539,17 +5539,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.102.026-0</t>
+          <t>61.101.080-K</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2854.81</v>
+        <v>3320.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3412-246-CM25</t>
+          <t>3229-10368-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5604,17 +5604,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.101.080-K</t>
+          <t>61.102.026-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3320.78</v>
+        <v>2854.81</v>
       </c>
     </row>
     <row r="81">
@@ -6364,7 +6364,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>707427-17-CM26</t>
+          <t>517903-28-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6384,17 +6384,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.114.000-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3430.73</v>
+        <v>117275.14</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>517903-28-CM26</t>
+          <t>707427-17-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.114.000-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>117275.14</v>
+        <v>3430.73</v>
       </c>
     </row>
     <row r="94">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7659,6 +7659,331 @@
       </c>
       <c r="M111" s="2" t="n">
         <v>1642.93</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1536-225-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>60.511.123-8</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>76.045.081-2</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>967.8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1079445-681-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>60.505.628-8</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>2277.66</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1079445-680-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>60.505.628-8</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>5379.41</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1079445-679-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>60.505.628-8</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>12204.45</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>764-252-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>60.511.120-3</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>1902.77</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes.xlsx
@@ -7619,7 +7619,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
